--- a/data/production/production_2026-W40.xlsx
+++ b/data/production/production_2026-W40.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -488,12 +488,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU-434367</t>
+          <t>AU-207096</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Clara Haines</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -503,11 +503,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1305.65</v>
+        <v>1928.72</v>
       </c>
     </row>
     <row r="5">
@@ -521,17 +521,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HO-361250</t>
+          <t>CM-853134</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zoe Marsh</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3024.69</v>
+        <v>4852.05</v>
       </c>
     </row>
     <row r="6">
@@ -549,17 +549,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LF-679720</t>
+          <t>LF-143978</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Theo Moreau</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -572,10 +572,8 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>$940.03</t>
-        </is>
+      <c r="G6" t="n">
+        <v>1199.34</v>
       </c>
     </row>
     <row r="7">
@@ -584,22 +582,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Maya Chen</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HO-114463</t>
+          <t>AU-728075</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Samuel Ruiz</t>
+          <t>Sofia Marsh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -608,7 +606,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1135.05</v>
+        <v>1448.07</v>
       </c>
     </row>
     <row r="8">
@@ -622,17 +620,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HO-356355</t>
+          <t>HO-516336</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Ivy Okafor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -641,7 +639,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2877.58</v>
+        <v>2851.21</v>
       </c>
     </row>
     <row r="9">
@@ -650,22 +648,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HO-425236</t>
+          <t>AU-530656</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owen Petrov</t>
+          <t>Sofia Pryor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -674,7 +672,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1920.54</v>
+        <v>1023.54</v>
       </c>
     </row>
     <row r="10">
@@ -683,17 +681,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Priya Raman</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CM-384434</t>
+          <t>CM-193749</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Marcus Ibsen</t>
+          <t>Ruby Ferreira</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -703,11 +701,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve">Renewal </t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7582.12</v>
+        <v>4406.79</v>
       </c>
     </row>
     <row r="11">
@@ -716,58 +714,90 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Priya Raman</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CM-966789</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nora Ruiz</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>$4,979.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Tom Becker</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AU-451291</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ivy Okafor</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1712.32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AU-215808</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ruby Ferreira</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Auto</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2205.38</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AU-947312</t>
+          <t>LF-748216</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maria Novak</t>
+          <t>Zoe Marsh</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t xml:space="preserve">Life </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -776,7 +806,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1018.53</v>
+        <v>1121.34</v>
       </c>
     </row>
     <row r="14">
@@ -785,22 +815,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LF-986575</t>
+          <t>AU-138993</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Leah Novak</t>
+          <t>Samuel Brennan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -809,26 +839,26 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>776.75</v>
+        <v>2036.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AU-136332</t>
+          <t>AU-445801</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nora Ashby</t>
+          <t>Elena Novak</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -838,11 +868,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2364.31</v>
+        <v>1309.71</v>
       </c>
     </row>
     <row r="16">
@@ -851,31 +881,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AISHA BELLO</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AU-161437</t>
+          <t>HO-937660</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>James Whitfield</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t xml:space="preserve">Renewal </t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2243.65</v>
+        <v>1632.24</v>
       </c>
     </row>
     <row r="17">
@@ -889,26 +919,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AU-945372</t>
+          <t>AU-957836</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sofia Pryor</t>
+          <t>Mila Tanaka</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Auto</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1254.83</v>
+        <v>1075.24</v>
       </c>
     </row>
     <row r="18">
@@ -917,31 +947,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LF-695225</t>
+          <t>AU-700831</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>653.59</v>
+          <t>renewal</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>$1,990.26</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -955,12 +987,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AU-264951</t>
+          <t>AU-777314</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Samuel Ruiz</t>
+          <t>Adrian Okafor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -970,13 +1002,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>$1,750.33</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1116.83</v>
       </c>
     </row>
     <row r="20">
@@ -990,64 +1020,64 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AU-371840</t>
+          <t>CM-317771</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Elena Mbeki</t>
+          <t>Marcus Novak</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2110.37</v>
+        <v>4261.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AU-835575</t>
+          <t>LF-566775</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Leah Novak</t>
+          <t>Grace Delgado</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2049.08</v>
+        <v>681.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1056,59 +1086,61 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HO-946313</t>
+          <t>LF-285891</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Isaac Holloway</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1218.08</v>
+        <v>790.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LF-208998</t>
+          <t>HO-403380</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Samuel Ruiz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>home</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1314.92</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>$3,084.77</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1117,31 +1149,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HO-163941</t>
+          <t>LF-834898</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maria Ashby</t>
+          <t>Maria Moreau</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2318.39</v>
+        <v>855.6799999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1150,31 +1182,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t xml:space="preserve"> Priya Raman</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AU-668458</t>
+          <t>HO-537258</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Maria Duarte</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>2322.55</v>
+          <t xml:space="preserve"> Renewal</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>$2,076.70</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1183,22 +1217,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t xml:space="preserve">Priya Raman </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AU-631219</t>
+          <t>HO-790808</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Victor Petrov</t>
+          <t>Maria Moreau</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1207,7 +1241,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2283.87</v>
+        <v>3180.48</v>
       </c>
     </row>
     <row r="27">
@@ -1216,31 +1250,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HO-544150</t>
+          <t>HO-136811</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Marcus Novak</t>
+          <t>Maria Duarte</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>2152.2</v>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>$1,819.30</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1249,12 +1285,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>tom becker</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LF-238394</t>
+          <t>HO-156398</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1264,82 +1300,82 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2602.04</v>
+        <v>2409.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CM-334026</t>
+          <t>LF-208996</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Adrian Okafor</t>
+          <t>Owen Petrov</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3175.53</v>
+        <v>660.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HO-162804</t>
+          <t>AU-776545</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maria Novak</t>
+          <t>Mila Tanaka</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1600.15</v>
+        <v>1653.06</v>
       </c>
     </row>
     <row r="31">
@@ -1348,31 +1384,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aisha Bello </t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LF-670968</t>
+          <t>HO-559691</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Marcus Ibsen</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1310.01</v>
+        <v>1277.19</v>
       </c>
     </row>
     <row r="32">
@@ -1381,22 +1417,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LF-204998</t>
+          <t>CM-604141</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Samuel Brennan</t>
+          <t>Leah Okafor</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1405,7 +1441,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2465.69</v>
+        <v>7267.3</v>
       </c>
     </row>
     <row r="33">
@@ -1414,36 +1450,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t xml:space="preserve">Tom Becker </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HO-102693</t>
+          <t>LF-677135</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Grace Delgado</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>renewal</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1342.2</v>
+        <v>2317.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1452,17 +1488,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HO-477617</t>
+          <t>AU-000000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Samuel Brennan</t>
+          <t>Pending entry</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1470,216 +1506,16 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>2141.91</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46297</v>
-      </c>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>maya chen</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AU-260097</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Clara Pryor</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Auto</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>New</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1704.85</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>maya chen</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LF-738407</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Samuel Brennan</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>820.37</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya Raman </t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CM-911102</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Grace Albright</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>$8,284.44</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AU-875501</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Nora Ashby</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>2158.98</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LF-214266</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Maria Novak</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>858.61</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Luis Ortega</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AU-000000</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Pending entry</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>74794.21000000001</v>
+        <v>67512.89999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1693,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,16 +1567,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LF-238394</t>
+          <t>HO-403380</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2374.46</v>
+        <v>2940.06</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1756,20 +1592,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HO-593894</t>
+          <t>CM-604141</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1462.82</v>
+        <v>7210.28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AU-835575</t>
+          <t>AU-776545</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1790,7 +1626,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1961.85</v>
+        <v>1570.11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1806,7 +1642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AU-371840</t>
+          <t>AU-700831</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1815,7 +1651,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2133.76</v>
+        <v>2010.94</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1831,16 +1667,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HO-946313</t>
+          <t>AU-777314</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1161.65</v>
+        <v>1146.87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1856,7 +1692,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CM-384434</t>
+          <t>CM-966789</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1865,7 +1701,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7181.87</v>
+        <v>4649.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1881,16 +1717,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CM-334026</t>
+          <t>HO-537258</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2842.37</v>
+        <v>1864.37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1906,7 +1742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CM-911102</t>
+          <t>CM-193749</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1915,7 +1751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8129.21</v>
+        <v>4127.17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1931,16 +1767,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AU-875501</t>
+          <t>HO-136811</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2076.76</v>
+        <v>1786.97</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1956,20 +1792,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LF-868043</t>
+          <t>AU-215808</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2074.18</v>
+        <v>2210.41</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1817,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LF-106687</t>
+          <t>LF-677135</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1990,11 +1826,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1065.74</v>
+        <v>2266.43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
@@ -2006,7 +1842,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AU-136332</t>
+          <t>AU-423400</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2015,11 +1851,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2225.14</v>
+        <v>2388.73</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -2031,16 +1867,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HO-163941</t>
+          <t>AU-207096</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2256.45</v>
+        <v>1848.56</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2056,7 +1892,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HO-361250</t>
+          <t>HO-937660</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2065,7 +1901,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2774.12</v>
+        <v>1650.19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2081,16 +1917,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LF-670968</t>
+          <t>CM-853134</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1282.31</v>
+        <v>4345.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2106,20 +1942,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LF-204998</t>
+          <t>HO-355012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2450.56</v>
+        <v>1988.62</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -2131,45 +1967,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HO-703656</t>
+          <t>AU-957836</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3090.39</v>
+        <v>960.47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CM-979988</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4806.23</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
